--- a/samples/table-spec/table-spec.xlsx
+++ b/samples/table-spec/table-spec.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-31T11:00:27+09:00</t>
+          <t>2026-10-31T19:10:52+09:00</t>
         </is>
       </c>
     </row>
